--- a/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9431_escuela-villa-san-miguel_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F3F874B-8547-4559-A32C-06A83FA7E1E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7E4FF82-25F7-443D-BA43-4F11A56761B6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6605F430-DC72-469F-9349-5E3F768CDDBE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09701C93-B44D-4E10-AFBC-B675F5288354}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B911A18-B9B7-42BA-AA8B-A3C144392A9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4A00420-114E-4234-8641-C60A399AB412}"/>
 </file>